--- a/OpenVPM/src/test/resources/testData.xlsx
+++ b/OpenVPM/src/test/resources/testData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\eclipse-workspace\OpenVPM\src\test\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\git\repositoryOpenVpm\OpenVPM\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA846754-12EF-4AD8-9340-C1ECB88253CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{211F66F4-3B1B-4A6E-87B3-EB40F34BFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15495" yWindow="1110" windowWidth="23010" windowHeight="12210" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Clients" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="176">
   <si>
     <t>First Name</t>
   </si>
@@ -526,6 +526,36 @@
   </si>
   <si>
     <t>VacciBordetella</t>
+  </si>
+  <si>
+    <t>03:30</t>
+  </si>
+  <si>
+    <t>03:00</t>
+  </si>
+  <si>
+    <t>04:00</t>
+  </si>
+  <si>
+    <t>04:30</t>
+  </si>
+  <si>
+    <t>05:00</t>
+  </si>
+  <si>
+    <t>05:30</t>
+  </si>
+  <si>
+    <t>Exam Room 4</t>
+  </si>
+  <si>
+    <t>Exam Room 5</t>
+  </si>
+  <si>
+    <t>Exam Room 6</t>
+  </si>
+  <si>
+    <t>Exam Room 7</t>
   </si>
 </sst>
 </file>
@@ -587,7 +617,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -869,14 +899,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -890,7 +920,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>40</v>
       </c>
@@ -904,7 +934,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>41</v>
       </c>
@@ -918,7 +948,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>42</v>
       </c>
@@ -932,7 +962,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>43</v>
       </c>
@@ -946,7 +976,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>44</v>
       </c>
@@ -960,7 +990,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>45</v>
       </c>
@@ -974,7 +1004,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>46</v>
       </c>
@@ -988,7 +1018,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>47</v>
       </c>
@@ -1002,7 +1032,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -1016,7 +1046,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>49</v>
       </c>
@@ -1038,18 +1068,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6912B02C-9683-4B22-8559-8CC00921B784}">
   <dimension ref="A1:H14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -1075,7 +1105,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>115</v>
       </c>
@@ -1101,7 +1131,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -1127,7 +1157,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>147</v>
       </c>
@@ -1153,7 +1183,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>148</v>
       </c>
@@ -1173,7 +1203,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>93</v>
       </c>
@@ -1193,7 +1223,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>94</v>
       </c>
@@ -1213,7 +1243,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>95</v>
       </c>
@@ -1233,7 +1263,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>96</v>
       </c>
@@ -1253,7 +1283,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>97</v>
       </c>
@@ -1273,7 +1303,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>98</v>
       </c>
@@ -1293,7 +1323,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>99</v>
       </c>
@@ -1313,7 +1343,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>100</v>
       </c>
@@ -1333,7 +1363,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>101</v>
       </c>
@@ -1361,16 +1391,16 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{032423CF-4F2B-490B-8768-3BF60D68F851}">
-  <dimension ref="A1:E15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -1387,7 +1417,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1404,7 +1434,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>10</v>
       </c>
@@ -1418,7 +1448,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>11</v>
       </c>
@@ -1432,7 +1462,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>12</v>
       </c>
@@ -1446,7 +1476,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>13</v>
       </c>
@@ -1457,52 +1487,94 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>14</v>
       </c>
+      <c r="D7" t="s">
+        <v>172</v>
+      </c>
       <c r="E7" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D8" t="s">
+        <v>173</v>
+      </c>
       <c r="E8" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D9" t="s">
+        <v>174</v>
+      </c>
       <c r="E9" s="2" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D10" t="s">
+        <v>175</v>
+      </c>
       <c r="E10" s="2" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E11" s="2" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E12" s="2" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E13" s="2" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E14" s="2" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E15" s="5" t="s">
         <v>156</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E16" s="5" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="17" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E17" s="5" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="18" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E18" s="5" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="19" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E19" s="5" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="20" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E20" s="5" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="21" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E21" s="5" t="s">
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -1513,13 +1585,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF1944C6-9E51-4456-9688-E61EFC28D07E}">
   <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>129</v>
       </c>
@@ -1527,7 +1599,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>130</v>
       </c>
@@ -1535,7 +1607,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1543,7 +1615,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>131</v>
       </c>
@@ -1551,7 +1623,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>132</v>
       </c>
@@ -1559,7 +1631,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>133</v>
       </c>
@@ -1567,7 +1639,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>134</v>
       </c>
@@ -1575,32 +1647,32 @@
         <v>146</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>9</v>
       </c>

--- a/OpenVPM/src/test/resources/testData.xlsx
+++ b/OpenVPM/src/test/resources/testData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\git\repositoryOpenVpm\OpenVPM\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{211F66F4-3B1B-4A6E-87B3-EB40F34BFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCF29B46-71EC-4FFA-9E03-4F4964EC5AD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Clients" sheetId="1" r:id="rId1"/>
@@ -489,18 +489,6 @@
     <t>Gregory</t>
   </si>
   <si>
-    <t>01:00</t>
-  </si>
-  <si>
-    <t>01:30</t>
-  </si>
-  <si>
-    <t>02:00</t>
-  </si>
-  <si>
-    <t>02:30</t>
-  </si>
-  <si>
     <t>Exam Room 3</t>
   </si>
   <si>
@@ -528,24 +516,6 @@
     <t>VacciBordetella</t>
   </si>
   <si>
-    <t>03:30</t>
-  </si>
-  <si>
-    <t>03:00</t>
-  </si>
-  <si>
-    <t>04:00</t>
-  </si>
-  <si>
-    <t>04:30</t>
-  </si>
-  <si>
-    <t>05:00</t>
-  </si>
-  <si>
-    <t>05:30</t>
-  </si>
-  <si>
     <t>Exam Room 4</t>
   </si>
   <si>
@@ -556,6 +526,36 @@
   </si>
   <si>
     <t>Exam Room 7</t>
+  </si>
+  <si>
+    <t>13:00</t>
+  </si>
+  <si>
+    <t>13:30</t>
+  </si>
+  <si>
+    <t>14:00</t>
+  </si>
+  <si>
+    <t>14:30</t>
+  </si>
+  <si>
+    <t>15:00</t>
+  </si>
+  <si>
+    <t>15:30</t>
+  </si>
+  <si>
+    <t>16:00</t>
+  </si>
+  <si>
+    <t>16:30</t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>17:30</t>
   </si>
 </sst>
 </file>
@@ -611,13 +611,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1099,10 +1098,10 @@
         <v>92</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>158</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -1125,10 +1124,10 @@
         <v>116</v>
       </c>
       <c r="G2" t="s">
+        <v>155</v>
+      </c>
+      <c r="H2" t="s">
         <v>159</v>
-      </c>
-      <c r="H2" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -1151,10 +1150,10 @@
         <v>117</v>
       </c>
       <c r="G3" t="s">
+        <v>156</v>
+      </c>
+      <c r="H3" t="s">
         <v>160</v>
-      </c>
-      <c r="H3" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -1177,10 +1176,10 @@
         <v>118</v>
       </c>
       <c r="G4" t="s">
+        <v>157</v>
+      </c>
+      <c r="H4" t="s">
         <v>161</v>
-      </c>
-      <c r="H4" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -1481,7 +1480,7 @@
         <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>26</v>
@@ -1492,7 +1491,7 @@
         <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>27</v>
@@ -1500,7 +1499,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D8" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>28</v>
@@ -1508,7 +1507,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D9" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>149</v>
@@ -1516,7 +1515,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D10" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>150</v>
@@ -1529,52 +1528,52 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E12" s="2" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E13" s="2" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E14" s="2" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E15" s="5" t="s">
-        <v>156</v>
+      <c r="E15" s="2" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E16" s="5" t="s">
-        <v>167</v>
+      <c r="E16" s="2" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="17" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E17" s="5" t="s">
-        <v>166</v>
+      <c r="E17" s="2" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="18" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E18" s="5" t="s">
-        <v>168</v>
+      <c r="E18" s="2" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="19" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E19" s="5" t="s">
-        <v>169</v>
+      <c r="E19" s="2" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="20" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E20" s="5" t="s">
-        <v>170</v>
+      <c r="E20" s="2" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="21" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E21" s="5" t="s">
-        <v>171</v>
+      <c r="E21" s="2" t="s">
+        <v>175</v>
       </c>
     </row>
   </sheetData>
